--- a/artfynd/A 36452-2026 artfynd.xlsx
+++ b/artfynd/A 36452-2026 artfynd.xlsx
@@ -1100,7 +1100,7 @@
         <v>136384831</v>
       </c>
       <c r="B5" t="n">
-        <v>111317</v>
+        <v>111324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36452-2026 artfynd.xlsx
+++ b/artfynd/A 36452-2026 artfynd.xlsx
@@ -1100,7 +1100,7 @@
         <v>136384831</v>
       </c>
       <c r="B5" t="n">
-        <v>111324</v>
+        <v>111325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36452-2026 artfynd.xlsx
+++ b/artfynd/A 36452-2026 artfynd.xlsx
@@ -822,7 +822,7 @@
         <v>136384084</v>
       </c>
       <c r="B3" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136384831</v>
       </c>
       <c r="B5" t="n">
-        <v>111325</v>
+        <v>111330</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136383564</v>
       </c>
       <c r="B8" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136383854</v>
       </c>
       <c r="B9" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36452-2026 artfynd.xlsx
+++ b/artfynd/A 36452-2026 artfynd.xlsx
@@ -1100,7 +1100,7 @@
         <v>136384831</v>
       </c>
       <c r="B5" t="n">
-        <v>111330</v>
+        <v>111332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36452-2026 artfynd.xlsx
+++ b/artfynd/A 36452-2026 artfynd.xlsx
@@ -1100,7 +1100,7 @@
         <v>136384831</v>
       </c>
       <c r="B5" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36452-2026 artfynd.xlsx
+++ b/artfynd/A 36452-2026 artfynd.xlsx
@@ -1100,7 +1100,7 @@
         <v>136384831</v>
       </c>
       <c r="B5" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36452-2026 artfynd.xlsx
+++ b/artfynd/A 36452-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1698,10 +1698,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112997469</v>
+        <v>137439566</v>
       </c>
       <c r="B10" t="n">
-        <v>5179</v>
+        <v>58032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,46 +1709,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Digerberget, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501775</v>
+        <v>501753</v>
       </c>
       <c r="R10" t="n">
-        <v>6594581</v>
+        <v>6594554</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1772,12 +1771,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1786,56 +1785,30 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # två torrgranar # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112997469</t>
+          <t>https://artportalen.se/Sighting/137439566</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112997472</v>
+        <v>112997469</v>
       </c>
       <c r="B11" t="n">
         <v>5179</v>
@@ -1879,10 +1852,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501768</v>
+        <v>501775</v>
       </c>
       <c r="R11" t="n">
-        <v>6594555</v>
+        <v>6594581</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1949,7 +1922,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # en torrgran # Picea abies</t>
+          <t>Standing dead tree/snags # två torrgranar # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1966,7 +1939,589 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/112997469</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>112997472</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Digerberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>501768</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6594555</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # en torrgran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/112997472</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137439562</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58476</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Digerberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>501753</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6594554</v>
+      </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137439562</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137439565</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58471</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Digerberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>501753</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6594554</v>
+      </c>
+      <c r="S14" t="n">
+        <v>100</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137439565</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137439567</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58196</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Digerberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>501753</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6594554</v>
+      </c>
+      <c r="S15" t="n">
+        <v>100</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137439567</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137445704</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58191</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Digerberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>501753</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6594554</v>
+      </c>
+      <c r="S16" t="n">
+        <v>100</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137445704</t>
         </is>
       </c>
     </row>
@@ -1982,6 +2537,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36452-2026 artfynd.xlsx
+++ b/artfynd/A 36452-2026 artfynd.xlsx
@@ -1701,7 +1701,7 @@
         <v>137439566</v>
       </c>
       <c r="B10" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>137439562</v>
       </c>
       <c r="B13" t="n">
-        <v>58476</v>
+        <v>58479</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>137439565</v>
       </c>
       <c r="B14" t="n">
-        <v>58471</v>
+        <v>58474</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>137439567</v>
       </c>
       <c r="B15" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>137445704</v>
       </c>
       <c r="B16" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
